--- a/build/gider_sablon.xlsx
+++ b/build/gider_sablon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://odaktedarik-my.sharepoint.com/personal/gorkem_cadirci_odaklojistik_com_tr/Documents/Masaüstü/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{C0549C2B-CA03-4C5A-98B6-2243AD371C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E84D343-0B46-4438-8DE7-FE153AA6D684}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C73B1432-6357-4AA8-A725-F7EBBAC4F4F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ŞABLON" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="141">
   <si>
     <t>SeferID</t>
   </si>
@@ -441,6 +441,9 @@
   </si>
   <si>
     <t>ÇİFT SÜRÜCÜ BEDELİ</t>
+  </si>
+  <si>
+    <t>ARA TAŞIMA</t>
   </si>
 </sst>
 </file>
@@ -871,7 +874,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.8984375" customWidth="1"/>
@@ -1846,6 +1849,20 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>2</v>
+      </c>
+      <c r="B70">
+        <v>26</v>
+      </c>
+      <c r="C70" t="s">
+        <v>140</v>
+      </c>
+      <c r="D70" s="1">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
